--- a/data/trans_camb/IP09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 61,09</t>
+          <t>1,77; 58,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 50,14</t>
+          <t>-17,52; 47,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,81; 93,04</t>
+          <t>15,75; 91,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 46,43</t>
+          <t>-6,41; 48,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 49,29</t>
+          <t>-11,32; 51,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 26,34</t>
+          <t>-24,76; 29,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 48,25</t>
+          <t>6,96; 46,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 39,3</t>
+          <t>-4,85; 40,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 61,29</t>
+          <t>-1,56; 61,18</t>
         </is>
       </c>
     </row>
@@ -798,39 +798,39 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 756,64</t>
+          <t>-30,53; 967,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,82; —</t>
+          <t>-59,79; 991,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 467,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,54; 1078,2</t>
+          <t>13,92; 913,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 762,48</t>
+          <t>-34,3; 630,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 1371,38</t>
+          <t>-23,34; 1299,59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 32,74</t>
+          <t>-36,62; 33,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 67,56</t>
+          <t>-12,09; 68,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-59,01; 15,04</t>
+          <t>-56,26; 12,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 57,09</t>
+          <t>-3,77; 56,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 83,27</t>
+          <t>-5,42; 83,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 64,96</t>
+          <t>-0,13; 65,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 35,85</t>
+          <t>-8,99; 36,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 67,77</t>
+          <t>3,52; 69,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 33,78</t>
+          <t>-17,9; 35,13</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,87; 122,92</t>
+          <t>-57,19; 134,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 282,66</t>
+          <t>-11,61; 288,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,36</t>
+          <t>-100,0; 81,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 1043,98</t>
+          <t>-21,62; 1000,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,29 +1024,29 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 1161,11</t>
+          <t>-15,8; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 212,29</t>
+          <t>-22,83; 198,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,58; 406,34</t>
+          <t>12,93; 385,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 174,37</t>
+          <t>-49,39; 188,19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 38,17</t>
+          <t>-47,5; 36,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 65,13</t>
+          <t>-25,74; 72,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 39,27</t>
+          <t>-38,99; 38,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 40,42</t>
+          <t>-51,75; 41,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 0,0</t>
+          <t>-74,65; -12,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 43,2</t>
+          <t>-42,07; 43,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 25,55</t>
+          <t>-30,78; 26,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 31,84</t>
+          <t>-35,99; 31,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 33,28</t>
+          <t>-23,49; 31,87</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,22; —</t>
+          <t>-73,48; 425,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,16; 289,01</t>
+          <t>-72,64; 301,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 558,06</t>
+          <t>-100,0; 471,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 410,97</t>
+          <t>-56,08; 310,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 72,16</t>
+          <t>-8,25; 72,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 60,67</t>
+          <t>-2,73; 57,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 53,02</t>
+          <t>-8,0; 54,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 9,37</t>
+          <t>-56,34; 8,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 49,76</t>
+          <t>-32,97; 45,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 8,11</t>
+          <t>-59,2; 4,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 26,83</t>
+          <t>-22,74; 27,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 44,47</t>
+          <t>-6,33; 44,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 17,77</t>
+          <t>-29,41; 15,62</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,29; —</t>
+          <t>-71,02; 472,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 425,14</t>
+          <t>-100,0; 511,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 787,64</t>
+          <t>-39,1; 661,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-89,17; 203,38</t>
+          <t>-88,83; 242,43</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 32,3</t>
+          <t>-57,81; 32,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,37 +1551,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 29,91</t>
+          <t>-59,62; 30,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 60,25</t>
+          <t>-37,41; 55,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-85,67; -14,28</t>
+          <t>-85,65; -14,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 85,58</t>
+          <t>-11,95; 85,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 38,84</t>
+          <t>-26,01; 40,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-63,42; -13,37</t>
+          <t>-64,67; -14,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 53,3</t>
+          <t>-20,36; 55,99</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 486,49</t>
+          <t>-51,27; 386,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 599,53</t>
+          <t>-4,86; 600,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 259,39</t>
+          <t>-47,9; 274,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,14 +1687,14 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 320,0</t>
+          <t>-42,78; 302,18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-87,56; 25,58</t>
+          <t>-87,52; 25,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 72,11</t>
+          <t>-39,38; 80,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 30,62</t>
+          <t>-43,08; 31,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,82; 87,35</t>
+          <t>10,46; 87,47</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 32,69</t>
+          <t>-37,97; 37,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 18,24</t>
+          <t>-49,78; 16,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,54; 73,62</t>
+          <t>2,63; 70,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 15,07</t>
+          <t>-51,75; 10,42</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-46,95; —</t>
+          <t>-45,73; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,39 +1878,39 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15,43; —</t>
+          <t>22,39; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,55; —</t>
+          <t>-77,68; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-81,99; 155,77</t>
+          <t>-83,13; 150,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9,02; 711,39</t>
+          <t>3,35; 424,18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-84,73; 147,26</t>
+          <t>-86,48; 89,36</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>25,85; 68,73</t>
+          <t>25,8; 68,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,09</t>
+          <t>0,0; 55,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,05; 59,94</t>
+          <t>12,07; 61,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 16,08</t>
+          <t>-38,1; 13,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 13,94</t>
+          <t>-46,69; 13,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 22,63</t>
+          <t>-37,88; 19,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 31,69</t>
+          <t>-8,25; 30,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 17,99</t>
+          <t>-21,22; 19,74</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 27,79</t>
+          <t>-13,01; 26,85</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 84,83</t>
+          <t>-72,26; 58,5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,04</t>
+          <t>-87,53; 63,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,2; 93,65</t>
+          <t>-70,56; 84,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 269,38</t>
+          <t>-28,14; 245,52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 140,68</t>
+          <t>-70,39; 143,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 207,14</t>
+          <t>-40,52; 206,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 19,57</t>
+          <t>-31,01; 19,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 40,44</t>
+          <t>-26,72; 40,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,46; 66,9</t>
+          <t>4,35; 69,09</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 22,07</t>
+          <t>-21,69; 19,61</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,7; 67,59</t>
+          <t>10,44; 66,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 56,18</t>
+          <t>-17,95; 53,66</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 13,29</t>
+          <t>-21,07; 12,33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,31; 48,12</t>
+          <t>0,21; 47,12</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,85; 52,05</t>
+          <t>6,89; 53,38</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 205,14</t>
+          <t>-74,63; 185,6</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,69; 377,52</t>
+          <t>-71,54; 359,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4,19; 571,89</t>
+          <t>7,7; 592,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 122,29</t>
+          <t>-55,13; 117,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,16; 383,83</t>
+          <t>32,17; 423,87</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 287,53</t>
+          <t>-47,91; 272,26</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 66,42</t>
+          <t>-55,66; 67,89</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>7,87; 246,17</t>
+          <t>-3,64; 231,24</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11,7; 254,46</t>
+          <t>19,96; 257,86</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 24,55</t>
+          <t>-0,71; 23,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,15; 30,69</t>
+          <t>3,92; 31,46</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,44; 33,59</t>
+          <t>1,71; 36,06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 15,9</t>
+          <t>-6,24; 15,23</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,46; 30,91</t>
+          <t>4,58; 30,36</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 13,15</t>
+          <t>-12,25; 12,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 16,68</t>
+          <t>-1,39; 15,4</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>7,24; 28,02</t>
+          <t>6,05; 26,69</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 18,29</t>
+          <t>-3,49; 17,74</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 162,37</t>
+          <t>-3,05; 147,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>8,12; 191,37</t>
+          <t>10,14; 185,73</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 199,92</t>
+          <t>2,11; 214,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 67,06</t>
+          <t>-17,27; 68,12</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,96; 132,31</t>
+          <t>12,38; 127,46</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 55,18</t>
+          <t>-36,24; 52,1</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 79,17</t>
+          <t>-4,63; 70,76</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>22,02; 125,12</t>
+          <t>20,67; 120,79</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 83,37</t>
+          <t>-11,99; 76,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 58,98</t>
+          <t>2,78; 61,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 47,32</t>
+          <t>-19,69; 51,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 91,79</t>
+          <t>14,88; 94,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 48,79</t>
+          <t>-5,88; 51,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 51,38</t>
+          <t>-11,34; 51,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 29,67</t>
+          <t>-24,33; 28,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 46,92</t>
+          <t>5,33; 46,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 40,18</t>
+          <t>-5,88; 39,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 61,18</t>
+          <t>2,53; 62,37</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 967,44</t>
+          <t>-28,9; 791,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,79; 991,85</t>
+          <t>-54,65; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 913,22</t>
+          <t>9,54; 972,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 630,45</t>
+          <t>-35,51; 762,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 1299,59</t>
+          <t>-27,41; 1462,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 33,95</t>
+          <t>-38,76; 31,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 68,7</t>
+          <t>-17,82; 65,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 12,32</t>
+          <t>-58,79; 15,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 56,26</t>
+          <t>-5,17; 56,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 83,45</t>
+          <t>-15,46; 83,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 65,1</t>
+          <t>1,06; 66,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 36,97</t>
+          <t>-9,73; 35,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 69,47</t>
+          <t>7,66; 69,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 35,13</t>
+          <t>-19,07; 31,31</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 134,22</t>
+          <t>-58,4; 124,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 288,15</t>
+          <t>-17,5; 223,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 81,93</t>
+          <t>-100,0; 102,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 1000,05</t>
+          <t>-30,8; 1020,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1312,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,8; —</t>
+          <t>-15,18; 1191,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 198,57</t>
+          <t>-23,43; 182,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,93; 385,7</t>
+          <t>22,22; 395,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,39; 188,19</t>
+          <t>-47,18; 163,96</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 36,82</t>
+          <t>-44,64; 36,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 72,85</t>
+          <t>-30,37; 67,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 38,14</t>
+          <t>-38,83; 37,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-51,75; 41,17</t>
+          <t>-51,41; 40,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 43,27</t>
+          <t>-48,03; 41,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 26,76</t>
+          <t>-32,79; 26,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 31,72</t>
+          <t>-33,87; 34,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 31,87</t>
+          <t>-25,61; 31,7</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 425,67</t>
+          <t>-78,92; 341,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-72,64; 301,5</t>
+          <t>-73,04; 305,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 471,38</t>
+          <t>-100,0; 578,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 310,46</t>
+          <t>-63,2; 316,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 72,03</t>
+          <t>-8,4; 71,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 57,67</t>
+          <t>-0,74; 61,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 54,46</t>
+          <t>-8,48; 55,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-56,34; 8,64</t>
+          <t>-49,7; 9,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 45,44</t>
+          <t>-24,17; 47,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 4,23</t>
+          <t>-56,75; 6,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 27,92</t>
+          <t>-23,83; 26,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 44,76</t>
+          <t>-7,29; 43,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 15,62</t>
+          <t>-31,72; 16,31</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,02; 472,82</t>
+          <t>-57,12; 643,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 511,59</t>
+          <t>-85,35; 550,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 661,43</t>
+          <t>-26,0; 660,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,83; 242,43</t>
+          <t>-89,35; 215,64</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 32,59</t>
+          <t>-58,82; 33,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,37 +1551,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-59,62; 30,32</t>
+          <t>-59,99; 30,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 55,75</t>
+          <t>-33,68; 60,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-85,65; -14,28</t>
+          <t>-85,67; -14,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 85,61</t>
+          <t>-2,55; 85,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 40,93</t>
+          <t>-27,39; 41,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-64,67; -14,05</t>
+          <t>-61,45; -13,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 55,99</t>
+          <t>-19,75; 53,36</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 386,18</t>
+          <t>-47,18; 412,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 600,0</t>
+          <t>-3,15; 600,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 274,93</t>
+          <t>-51,15; 277,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 302,18</t>
+          <t>-40,18; 327,6</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-87,52; 25,59</t>
+          <t>-92,38; 25,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 80,63</t>
+          <t>-38,93; 80,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 31,96</t>
+          <t>-47,8; 30,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,46; 87,47</t>
+          <t>11,33; 87,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 37,39</t>
+          <t>-38,73; 33,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 16,76</t>
+          <t>-46,76; 18,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,63; 70,52</t>
+          <t>2,7; 72,4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-51,75; 10,42</t>
+          <t>-50,68; 15,95</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-45,73; —</t>
+          <t>-39,2; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22,39; —</t>
+          <t>18,68; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,68; —</t>
+          <t>-77,73; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 150,86</t>
+          <t>-83,73; 187,62</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,35; 424,18</t>
+          <t>6,4; 715,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 89,36</t>
+          <t>-82,47; 156,86</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>25,8; 68,72</t>
+          <t>25,91; 68,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,17</t>
+          <t>0,0; 46,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,07; 61,85</t>
+          <t>12,02; 58,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-38,1; 13,99</t>
+          <t>-39,96; 16,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 13,83</t>
+          <t>-46,45; 12,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 19,79</t>
+          <t>-35,17; 22,75</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 30,68</t>
+          <t>-9,29; 29,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 19,74</t>
+          <t>-24,25; 16,98</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 26,85</t>
+          <t>-14,81; 26,3</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-72,26; 58,5</t>
+          <t>-75,04; 71,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-87,53; 63,66</t>
+          <t>-100,0; 65,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 84,02</t>
+          <t>-65,8; 108,32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 245,52</t>
+          <t>-29,1; 224,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-70,39; 143,42</t>
+          <t>-77,77; 116,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 206,97</t>
+          <t>-40,68; 198,74</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 19,06</t>
+          <t>-33,52; 16,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 40,4</t>
+          <t>-26,66; 41,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,35; 69,09</t>
+          <t>2,92; 68,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 19,61</t>
+          <t>-20,37; 20,03</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10,44; 66,74</t>
+          <t>11,55; 68,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 53,66</t>
+          <t>-15,32; 54,29</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 12,33</t>
+          <t>-20,02; 13,12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,21; 47,12</t>
+          <t>0,7; 46,87</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,89; 53,38</t>
+          <t>6,08; 53,34</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 185,6</t>
+          <t>-76,19; 161,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-71,54; 359,95</t>
+          <t>-73,31; 308,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7,7; 592,78</t>
+          <t>0,12; 539,6</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 117,49</t>
+          <t>-55,61; 113,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>32,17; 423,87</t>
+          <t>29,31; 436,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 272,26</t>
+          <t>-46,11; 273,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 67,89</t>
+          <t>-51,38; 69,6</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 231,24</t>
+          <t>4,31; 241,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>19,96; 257,86</t>
+          <t>20,12; 272,55</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 23,39</t>
+          <t>-0,74; 23,05</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,92; 31,46</t>
+          <t>3,13; 33,18</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,71; 36,06</t>
+          <t>1,73; 37,29</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 15,23</t>
+          <t>-6,33; 16,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,58; 30,36</t>
+          <t>3,73; 31,16</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 12,94</t>
+          <t>-11,9; 13,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 15,4</t>
+          <t>-0,83; 15,45</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>6,05; 26,69</t>
+          <t>8,1; 28,92</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 17,74</t>
+          <t>-3,14; 17,86</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 147,02</t>
+          <t>-4,51; 144,58</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10,14; 185,73</t>
+          <t>8,77; 204,64</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2,11; 214,68</t>
+          <t>1,81; 222,99</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 68,12</t>
+          <t>-18,19; 71,91</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>12,38; 127,46</t>
+          <t>12,24; 137,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 52,1</t>
+          <t>-36,6; 56,23</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 70,76</t>
+          <t>-3,04; 70,84</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>20,67; 120,79</t>
+          <t>26,08; 133,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 76,84</t>
+          <t>-10,86; 77,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>37,47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>17,39</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>56,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,88</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>34,88</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26,49</t>
+          <t>13,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 61,06</t>
+          <t>-9,0; 46,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 51,46</t>
+          <t>-11,81; 49,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 94,64</t>
+          <t>-25,75; 26,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 51,31</t>
+          <t>4,76; 61,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 51,83</t>
+          <t>-16,53; 50,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 28,23</t>
+          <t>-3,76; 69,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 46,42</t>
+          <t>8,39; 48,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 39,86</t>
+          <t>-7,77; 39,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 62,37</t>
+          <t>-8,23; 35,13</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>126,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>100,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>365,03%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>169,4%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>546,13%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>126,04%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,05%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>339,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>173,25%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-39,73; 756,64</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-48,82; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 471,48</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-28,9; 791,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-54,65; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 972,42</t>
+          <t>21,54; 1078,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 762,8</t>
+          <t>-39,89; 762,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 1462,41</t>
+          <t>-39,54; 716,67</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42,28</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,47</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,64</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>36,21</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-26,38</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>42,28</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,1</t>
+          <t>-28,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,56</t>
+          <t>5,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 31,7</t>
+          <t>-1,98; 57,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 65,59</t>
+          <t>-13,15; 83,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 15,66</t>
+          <t>-2,12; 67,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 56,73</t>
+          <t>-38,56; 32,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 83,4</t>
+          <t>-9,5; 67,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 66,72</t>
+          <t>-59,84; 11,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 35,79</t>
+          <t>-9,6; 35,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 69,91</t>
+          <t>7,37; 67,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 31,31</t>
+          <t>-19,25; 32,55</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>178,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>254,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>225,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-7,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>76,77%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-55,93%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>178,64%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>254,72%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>211,49%</t>
+          <t>-59,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,4; 124,33</t>
+          <t>-32,77; 1043,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 223,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,09</t>
+          <t>-23,48; 1256,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 1020,94</t>
+          <t>-61,87; 122,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1312,82</t>
+          <t>-9,51; 282,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 1191,13</t>
+          <t>-100,0; 87,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 182,76</t>
+          <t>-23,26; 212,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,22; 395,53</t>
+          <t>24,58; 406,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 163,96</t>
+          <t>-48,85; 168,25</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,82</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-37,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>17,4</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-37,15</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>10,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,96</t>
+          <t>6,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 36,76</t>
+          <t>-51,35; 40,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 67,04</t>
+          <t>-74,67; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 37,67</t>
+          <t>-39,44; 42,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 40,13</t>
+          <t>-38,8; 38,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,65; -12,09</t>
+          <t>-30,56; 65,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 41,51</t>
+          <t>-35,85; 44,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 26,39</t>
+          <t>-32,09; 25,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 34,11</t>
+          <t>-37,99; 31,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 31,7</t>
+          <t>-22,82; 33,99</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-12,98%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>48,1%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>112,69%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48,63%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-12,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>-73,13; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-78,92; 341,98</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,04; 305,89</t>
+          <t>-77,16; 289,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 578,04</t>
+          <t>-100,0; 558,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,2; 316,86</t>
+          <t>-56,76; 429,83</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-19,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-19,9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>28,83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>29,43</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>21,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-19,61</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,22</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-20,44</t>
+          <t>22,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-2,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 71,35</t>
+          <t>-49,2; 9,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 61,04</t>
+          <t>-25,24; 49,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 55,5</t>
+          <t>-53,25; 8,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 9,38</t>
+          <t>-8,34; 72,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 47,41</t>
+          <t>0,72; 60,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-56,75; 6,24</t>
+          <t>-7,43; 52,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 26,53</t>
+          <t>-26,5; 26,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 43,66</t>
+          <t>-6,35; 44,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 16,31</t>
+          <t>-25,77; 20,27</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-69,87%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-70,93%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>361,81%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>369,33%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>267,62%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-69,87%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>39,97%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-72,85%</t>
+          <t>284,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-24,81%</t>
+          <t>-14,93%</t>
         </is>
       </c>
     </row>
@@ -1436,24 +1436,24 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>-61,29; —</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-57,12; 643,57</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,35; 550,36</t>
+          <t>-100,0; 425,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 660,21</t>
+          <t>-23,84; 787,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-89,35; 215,64</t>
+          <t>-84,55; 252,89</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16,48</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-43,12</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42,48</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-13,27</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-29,61</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-15,17</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16,48</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-43,12</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,7</t>
+          <t>-13,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,62</t>
+          <t>18,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 33,63</t>
+          <t>-28,73; 60,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>-85,67; -14,28</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>-3,7; 85,17</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-59,15; 32,3</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-59,99; 30,59</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>-33,68; 60,88</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-85,67; -14,27</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 85,6</t>
+          <t>-57,89; 32,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 41,49</t>
+          <t>-28,78; 38,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-61,45; -13,27</t>
+          <t>-63,42; -13,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 53,36</t>
+          <t>-19,59; 52,91</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-44,81%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-51,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-45,56%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -1647,37 +1647,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>-40,41; 486,49</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-4,6; 599,53</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-47,18; 412,37</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 600,62</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-51,15; 277,55</t>
+          <t>-52,53; 259,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,18; 327,6</t>
+          <t>-38,06; 320,43</t>
         </is>
       </c>
     </row>
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,6</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>61,44</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3,53</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-42,26</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>3,79</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-67,71</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>61,44</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>-13,95</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-17,3</t>
+          <t>-18,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-92,38; 25,42</t>
+          <t>-40,52; 30,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 80,71</t>
+          <t>3,82; 87,35</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>-39,21; 34,26</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>-87,56; 25,58</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>-46,62; 72,11</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>-100,0; 0,0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>-47,8; 30,44</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 87,54</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-38,73; 33,43</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 18,81</t>
+          <t>-50,56; 18,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,7; 72,4</t>
+          <t>5,54; 73,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 15,95</t>
+          <t>-54,15; 14,99</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-10,27%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>242,14%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-62,41%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>5,59%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-10,27%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>242,14%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>-36,93%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-45,82%</t>
+          <t>-47,81%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-39,2; —</t>
+          <t>15,43; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>-77,84; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-46,95; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>18,68; —</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-77,73; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-83,73; 187,62</t>
+          <t>-81,99; 155,77</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6,4; 715,8</t>
+          <t>9,02; 711,39</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,47; 156,86</t>
+          <t>-85,21; 150,24</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-12,37</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-18,06</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-7,47</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>47,35</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>18,12</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>32,1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-12,37</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-18,06</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,72</t>
+          <t>30,78</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,7</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>25,91; 68,68</t>
+          <t>-37,79; 16,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,3</t>
+          <t>-48,79; 13,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,02; 58,85</t>
+          <t>-34,07; 23,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 16,35</t>
+          <t>25,85; 68,73</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 12,75</t>
+          <t>0,0; 57,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 22,75</t>
+          <t>11,33; 59,7</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 29,47</t>
+          <t>-8,53; 31,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 16,98</t>
+          <t>-23,96; 17,99</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 26,3</t>
+          <t>-12,66; 28,97</t>
         </is>
       </c>
     </row>
@@ -2026,34 +2026,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-31,19%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-45,55%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-18,83%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-31,19%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-45,55%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-21,99%</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>48,65%</t>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>-73,36; 84,83</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 67,04</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>-65,32; 108,3</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-75,04; 71,35</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 65,65</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-65,8; 108,32</t>
-        </is>
-      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 224,62</t>
+          <t>-24,74; 269,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-77,77; 116,13</t>
+          <t>-75,32; 140,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 198,74</t>
+          <t>-40,79; 211,11</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>41,17</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>19,39</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-6,03</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>7,28</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>39,54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>41,17</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>41,49</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>29,94</t>
+          <t>30,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 16,51</t>
+          <t>-20,9; 22,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 41,8</t>
+          <t>6,7; 67,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,92; 68,02</t>
+          <t>-13,41; 56,91</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 20,03</t>
+          <t>-32,5; 19,57</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,55; 68,52</t>
+          <t>-25,36; 40,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 54,29</t>
+          <t>2,47; 68,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 13,12</t>
+          <t>-17,95; 13,29</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,7; 46,87</t>
+          <t>3,31; 48,12</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,08; 53,34</t>
+          <t>4,89; 52,71</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-2,73%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>139,76%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>65,82%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-21,86%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>26,4%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>143,37%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-2,73%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>139,76%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>150,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>103,85%</t>
+          <t>104,44%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-76,19; 161,79</t>
+          <t>-54,95; 122,29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-73,31; 308,55</t>
+          <t>19,16; 383,83</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0,12; 539,6</t>
+          <t>-41,39; 285,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 113,59</t>
+          <t>-73,61; 205,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>29,31; 436,66</t>
+          <t>-69,69; 377,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-46,11; 273,47</t>
+          <t>5,73; 599,16</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-51,38; 69,6</t>
+          <t>-51,59; 66,42</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>4,31; 241,07</t>
+          <t>7,87; 246,17</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>20,12; 272,55</t>
+          <t>10,36; 256,4</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>4,64</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>17,41</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2,35</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>11,51</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>17,72</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>15,31</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>17,41</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>5,43</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 23,05</t>
+          <t>-6,7; 15,9</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,13; 33,18</t>
+          <t>2,46; 30,91</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,73; 37,29</t>
+          <t>-11,24; 14,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 16,13</t>
+          <t>-0,73; 24,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,73; 31,16</t>
+          <t>2,15; 30,69</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 13,14</t>
+          <t>-3,26; 23,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 15,45</t>
+          <t>-0,29; 16,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>8,1; 28,92</t>
+          <t>7,24; 28,02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 17,86</t>
+          <t>-3,32; 15,17</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>60,46%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>50,56%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>77,88%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 144,58</t>
+          <t>-18,99; 67,06</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>8,77; 204,64</t>
+          <t>6,96; 132,31</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1,81; 222,99</t>
+          <t>-34,38; 59,91</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 71,91</t>
+          <t>-3,38; 162,37</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>12,24; 137,67</t>
+          <t>8,12; 191,37</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 56,23</t>
+          <t>-12,54; 153,47</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 70,84</t>
+          <t>-1,4; 79,17</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>26,08; 133,99</t>
+          <t>22,02; 125,12</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 77,03</t>
+          <t>-11,43; 67,79</t>
         </is>
       </c>
     </row>
